--- a/AmiAmi_sales.xlsx
+++ b/AmiAmi_sales.xlsx
@@ -58,9 +58,6 @@
     <t>Genshin Impact Eula: Wavecrest Waltz Ver. 1/7 Complete Figure</t>
   </si>
   <si>
-    <t>Blue Archive Wakamo (Swimsuit) 1/7 Complete Figure</t>
-  </si>
-  <si>
     <t>Blue Archive Kakudate Karin (Bunny Girl) 1/7 Complete Figure</t>
   </si>
   <si>
@@ -70,30 +67,33 @@
     <t>GODDESS OF VICTORY: NIKKE Cinderella 1/7 Complete Figure</t>
   </si>
   <si>
+    <t>Brown Dust 2 Morpeah: Daydream Bunny 1/7 Complete Figure</t>
+  </si>
+  <si>
     <t>[Bonus] Honkai: Star Rail Kafka 1/7 Complete Figure</t>
   </si>
   <si>
     <t>Monogatari Series Hitagi Senjougahara Remaster Project 1/7 Complete Figure</t>
   </si>
   <si>
-    <t>Brown Dust 2 Morpeah: Daydream Bunny 1/7 Complete Figure</t>
-  </si>
-  <si>
     <t>[Bonus] Genshin Impact Yae Miko, Astute Amusement Ver. 1/7 Complete Figure</t>
   </si>
   <si>
     <t>[Bonus] Zenless Zone Zero Ellen Joe 1/7 Complete Figure</t>
   </si>
   <si>
-    <t>Azur Lane Owari Anime Expo 2024 Ver. 1/7 Scale Figure</t>
-  </si>
-  <si>
     <t>GODDESS OF VICTORY: NIKKE Modernia - Second Affection 1/7 Complete Figure</t>
   </si>
   <si>
+    <t>GODDESS OF VICTORY: NIKKE Quency: Escape Queen 1/7 Complete Figure</t>
+  </si>
+  <si>
     <t>Character Vocal Series 01 Hatsune Miku 15th Anniversary Ver. 1/7 Complete Figure</t>
   </si>
   <si>
+    <t>Blue Archive Shiroko*Terror 1/7 Complete Figure</t>
+  </si>
+  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181987</t>
   </si>
   <si>
@@ -106,9 +106,6 @@
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181372</t>
   </si>
   <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-174926</t>
-  </si>
-  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-185231</t>
   </si>
   <si>
@@ -118,30 +115,33 @@
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-188732</t>
   </si>
   <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-195698</t>
+  </si>
+  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181818</t>
   </si>
   <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-189641</t>
   </si>
   <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-195698</t>
-  </si>
-  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-183456</t>
   </si>
   <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-187441</t>
   </si>
   <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-192157</t>
-  </si>
-  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-189651</t>
   </si>
   <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-191826</t>
+  </si>
+  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-190114</t>
   </si>
   <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-190380</t>
+  </si>
+  <si>
     <t>https://img.amiami.com/images/product/main/251/FIGURE-181987.jpg</t>
   </si>
   <si>
@@ -154,9 +154,6 @@
     <t>https://img.amiami.com/images/product/main/251/FIGURE-181372.jpg</t>
   </si>
   <si>
-    <t>https://img.amiami.com/images/product/main/243/FIGURE-174926.jpg</t>
-  </si>
-  <si>
     <t>https://img.amiami.com/images/product/main/252/FIGURE-185231.jpg</t>
   </si>
   <si>
@@ -166,31 +163,34 @@
     <t>https://img.amiami.com/images/product/main/253/FIGURE-188732.jpg</t>
   </si>
   <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-195698.jpg</t>
+  </si>
+  <si>
     <t>https://img.amiami.com/images/product/main/251/FIGURE-181818.jpg</t>
   </si>
   <si>
     <t>https://img.amiami.com/images/product/main/253/FIGURE-189641.jpg</t>
   </si>
   <si>
-    <t>https://img.amiami.com/images/product/main/254/FIGURE-195698.jpg</t>
-  </si>
-  <si>
     <t>https://img.amiami.com/images/product/main/251/FIGURE-183456.jpg</t>
   </si>
   <si>
     <t>https://img.amiami.com/images/product/main/253/FIGURE-187441.jpg</t>
   </si>
   <si>
-    <t>https://img.amiami.com/images/product/main/254/FIGURE-192157.jpg</t>
-  </si>
-  <si>
     <t>https://img.amiami.com/images/product/main/253/FIGURE-189651.jpg</t>
   </si>
   <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-191826.jpg</t>
+  </si>
+  <si>
     <t>https://img.amiami.com/images/product/main/253/FIGURE-190114.jpg</t>
   </si>
   <si>
-    <t>11,400 JPY</t>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-190380.jpg</t>
+  </si>
+  <si>
+    <t>14,280 JPY</t>
   </si>
   <si>
     <t>25,600 JPY</t>
@@ -202,9 +202,6 @@
     <t>19,980 JPY</t>
   </si>
   <si>
-    <t>20,160 JPY</t>
-  </si>
-  <si>
     <t>16,660 JPY</t>
   </si>
   <si>
@@ -226,15 +223,18 @@
     <t>21,000 JPY</t>
   </si>
   <si>
-    <t>26,120 JPY</t>
-  </si>
-  <si>
     <t>25,996 JPY</t>
   </si>
   <si>
+    <t>22,100 JPY</t>
+  </si>
+  <si>
     <t>42,895 JPY</t>
   </si>
   <si>
+    <t>23,562 JPY</t>
+  </si>
+  <si>
     <t>28,500 JPY</t>
   </si>
   <si>
@@ -247,9 +247,6 @@
     <t>30,580 JPY</t>
   </si>
   <si>
-    <t>28,800 JPY</t>
-  </si>
-  <si>
     <t>23,800 JPY</t>
   </si>
   <si>
@@ -274,10 +271,13 @@
     <t>26,800 JPY</t>
   </si>
   <si>
+    <t>22,600 JPY</t>
+  </si>
+  <si>
     <t>43,329 JPY</t>
   </si>
   <si>
-    <t>60.0%</t>
+    <t>49.89%</t>
   </si>
   <si>
     <t>35.35%</t>
@@ -307,10 +307,10 @@
     <t>6.42%</t>
   </si>
   <si>
-    <t>5.02%</t>
-  </si>
-  <si>
     <t>3.0%</t>
+  </si>
+  <si>
+    <t>2.21%</t>
   </si>
   <si>
     <t>1.0%</t>
@@ -839,7 +839,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>14</v>
@@ -857,7 +857,7 @@
         <v>77</v>
       </c>
       <c r="G7" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -880,7 +880,7 @@
         <v>78</v>
       </c>
       <c r="G8" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -903,7 +903,7 @@
         <v>79</v>
       </c>
       <c r="G9" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -920,10 +920,10 @@
         <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s">
         <v>93</v>
@@ -943,10 +943,10 @@
         <v>50</v>
       </c>
       <c r="E11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="G11" t="s">
         <v>93</v>
@@ -966,13 +966,13 @@
         <v>51</v>
       </c>
       <c r="E12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -995,7 +995,7 @@
         <v>82</v>
       </c>
       <c r="G13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -1018,7 +1018,7 @@
         <v>83</v>
       </c>
       <c r="G14" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -1038,10 +1038,10 @@
         <v>69</v>
       </c>
       <c r="F15" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G15" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1061,10 +1061,10 @@
         <v>70</v>
       </c>
       <c r="F16" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G16" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -1084,7 +1084,7 @@
         <v>71</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
         <v>98</v>

--- a/AmiAmi_sales.xlsx
+++ b/AmiAmi_sales.xlsx
@@ -10,14 +10,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$110</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="770" uniqueCount="570">
   <si>
     <t>Condition</t>
   </si>
@@ -40,52 +40,322 @@
     <t>Discount %</t>
   </si>
   <si>
+    <t>Pre-owned</t>
+  </si>
+  <si>
     <t>Sale</t>
   </si>
   <si>
     <t>New</t>
   </si>
   <si>
+    <t>Limited</t>
+  </si>
+  <si>
+    <t>TV Anime "Atelier Ryza: Ever Darkness &amp; the Secret Hideout" Reisalin Stout Dress Ver. 1/7 Figure</t>
+  </si>
+  <si>
+    <t>Kantai Collection -Kan Colle- Zuiho 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Brilliant Stage - THE IDOLM@STER S-3 Iori Minase 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>DreamTech THE IDOLM@STER Cinderella Girls [Uruwashi no Myouyaku] Kaede Takagaki + 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Love Live! School Idol Festival - Honoka Kosaka 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Kuma Kuma Kuma Bear Yuna 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Movie "The Quintessential Quintuplets" Ichika Nakano -Floral Dress Ver.- 1/7 Complete Figure (SHIBUYA SCRAMBLE FIGURE)</t>
+  </si>
+  <si>
+    <t>ARTFX - Star Wars: Darth Vader EP5 Ver. 1/7 Easy Assembly Kit</t>
+  </si>
+  <si>
+    <t>THE IDOLM@STER Cinderella Girls Kozue Yusa [Sweet Fairy] 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Battle! Costume Maid Watch Maid 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>RO-KYU-BU! SS - Airi Kashii -Kuro Usagi-san Ver.- 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Tomari Original Marinoa Truless 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Saekano: How to Raise a Boring Girlfriend Flat Izumi Hashima -Lingerie ver.- 1/7 Complete Figure (ANIPLEX+ Exclusive)</t>
+  </si>
+  <si>
+    <t>Original Character Assassin Niko 1/7 Complete Figure</t>
+  </si>
+  <si>
     <t>Yu-Gi-Oh! Card Game Monster Figure Collection Magician's Valkyria 1/7 Complete Figure</t>
   </si>
   <si>
+    <t>TV Anime "Hoshikuzu Telepath" "Yu Akeuchi" 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Azur Lane Takao: Divine Exorcist's Blade 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>7th Dragon 2020-II Samurai (Katanako) Maid Style 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>T.M.Revolution/Saekano: How to Raise a Boring Girlfriend Flat - Eriri Spencer Sawamura HOT LIMIT Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Yu-Gi-Oh! Card Game Monster Figure Collection Eria the Water Charmer 1/7 Complete Figure (Kotobukiya Shop Exclusive)</t>
+  </si>
+  <si>
+    <t>[Bonus] KDcolle Please Put Them On, Takamine-san - Takane Takamine Eternal Virgin Road Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>GODDESS OF VICTORY: NIKKE Modernia 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Original Character Officer Bunny 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Echocalypse Lilith Pure White Pledge Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>GRIDMAN DYNAZENON x Azur Lane Rikka Takarada: Blue Sky Station 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>ToHeart2 Dungeon Travelers - Tamaki Kosaka Samurai ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Girls' Frontline Welrod MkII 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>PRISMA WING So I'm a Spider, So What? Demon Lord Ariel 1/7 Complete Figure</t>
+  </si>
+  <si>
     <t>[Bonus] Honkai: Star Rail Dan Heng/Imbibitor Lunae DX Edition 1/7 Complete Figure</t>
   </si>
   <si>
+    <t>Honkai Impact 3rd Mei Raiden Herrscher of Thunder Aqueous Springtide Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Azur Lane Kearsarge All-Night Charge Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Ms. Vampire Who Lives in My Neighborhood Sophie Twilight 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Genshin Impact Eula: Wavecrest Waltz Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Fate Series - Idol Emperor/Nero 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Gakuen iDOLM@STER Kotone Fujita 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Princess Connect! Re:Dive Pecorine (Princess) 1/7 Complete Figure</t>
+  </si>
+  <si>
     <t>White Rabbit Rosu 1/7 Complete Figure</t>
   </si>
   <si>
-    <t>Genshin Impact Eula: Wavecrest Waltz Ver. 1/7 Complete Figure</t>
-  </si>
-  <si>
     <t>Blue Archive Kakudate Karin (Bunny Girl) 1/7 Complete Figure</t>
   </si>
   <si>
+    <t>GODDESS OF VICTORY: NIKKE Noir: Black Rabbit 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>hololive Hoshimachi Suisei 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>GODDESS OF VICTORY: NIKKE Rapunzel 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Slay the Gods Hong Ying Rosefire Plume 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Chang'e Yue Xi Lian Xiang. ver 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Arknights Hellagur Grand Ceremonial Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>The 7 Deadly Sins Maou Mokushiroku Gouman no Shou - Lucifer -Suikawari no Setsu- Regular Edition 1/7 Complete Figure [Monthly HobbyJAPAN Mail Order, Particular Shop Exclusive]</t>
+  </si>
+  <si>
+    <t>Love Live! Hasunosora Girls' High School Idol Club Kaho Hinoshita Fortune Movie Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>TV Anime "The Quintessential Quintuplets SS" "Miku Nakano Angel ver." 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Gakuen iDOLM@STER Hiro Shinosawa The thing I'm not good at Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>hololive Houshou Marine 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Azur Lane Ulrich von Hutten Ignition Matrician Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Getsuyoubi no Tawawa - "Ai-chan" 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Fate/Grand Order - Shielder/Mashu Kyrielite 1/7 Complete Figure [Aniplex+ Exclusive]</t>
+  </si>
+  <si>
+    <t>Girls' Frontline 1/7 Kar98k Roses in Hand Ver. Complete Figure</t>
+  </si>
+  <si>
+    <t>Sword Art Online the Movie: Ordinal Scale Asuna 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Sword Art Online Suguha Kirigaya White School Swimsuit ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Saekano: How to Raise a Boring Girlfriend Flat Megumi Kato 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Azur Lane Graf Zeppelin Beachside Urd Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Chainsaw Man Power &amp; Makima Nurse Ver. 1/7 Scale Figure set</t>
+  </si>
+  <si>
+    <t>That Time I Got Reincarnated as a Slime Milim Nava -Shutsugeki nano da!- 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Blue Archive Asuma Toki (Bunny Girl) 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Hell's Paradise: Jigokuraku Gabimaru 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Evangelion: 3.0 You Can [Not] Redo Rei Ayanami (Tentative Name) Plug Suit Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Azur Lane Taihou Enraptured Companion Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Magical Girl Lyrical Nanoha StrikerS - Nanoha Takamachi -Summer holiday- 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>"Rent-A-Girlfriend" Ruka Sarashina Bunny Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Umamusume Pretty Derby [White Wings Alight] Hokko Tarumae 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Ikkitousen GG - Unchou Kan-u School Swimsuit ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Hatsune Miku GT Project Racing Miku 2024Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Azur Lane Noshiro: Uncharted Festival Grounds? Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Saekano: How to Raise a Boring Girlfriend - Eriri Spencer Sawamura Hugging Pillow Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Kiss-Shot Acerola-Orion Heart-Under-Blade Kokorowatari Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Blue Archive Hanako (Swimsuit) 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>That Time I Got Reincarnated as a Slime Milim Nava Bunny Girl Style 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] KDcolle NUKITASHI THE ANIMATION Ikuko Onabuta 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Honkai: Star Rail Kafka 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Brown Dust 2 Morpeah: Daydream Bunny 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Monogatari Series Hitagi Senjougahara Remaster Project 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>"Nijisanji" Yang Nari 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Fate/stay night [Heaven's Feel] Saber Alter: Kimono ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[AmiAmi Exclusive Bonus] Shujuu Ecstasy Shion Oiran Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>NieR:Automata Ver1.1a A2 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>GODDESS OF VICTORY: NIKKE Quency: Escape Queen 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Genshin Impact Yae Miko, Astute Amusement Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>[Bonus] Zenless Zone Zero Ellen Joe 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Cat Eye Girl illustration by Freng 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Re:ZERO -Starting Life in Another World- Rem -Shiromuku- 1/7 Complete Figure</t>
+  </si>
+  <si>
     <t>hololive production Nakiri Ayame Shrine Maiden Fortune Outfit Ver. 1/7 Complete Figure</t>
   </si>
   <si>
-    <t>GODDESS OF VICTORY: NIKKE Cinderella 1/7 Complete Figure</t>
-  </si>
-  <si>
-    <t>Brown Dust 2 Morpeah: Daydream Bunny 1/7 Complete Figure</t>
-  </si>
-  <si>
-    <t>[Bonus] Honkai: Star Rail Kafka 1/7 Complete Figure</t>
-  </si>
-  <si>
-    <t>Monogatari Series Hitagi Senjougahara Remaster Project 1/7 Complete Figure</t>
-  </si>
-  <si>
-    <t>[Bonus] Genshin Impact Yae Miko, Astute Amusement Ver. 1/7 Complete Figure</t>
-  </si>
-  <si>
-    <t>[Bonus] Zenless Zone Zero Ellen Joe 1/7 Complete Figure</t>
+    <t>Azur Lane Owari Anime Expo 2024 Ver. 1/7 Scale Figure</t>
+  </si>
+  <si>
+    <t>Azur Lane Fritz Rumey Schwarzes Kaninchen Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Umamusume Pretty Derby Maruzensky Signature Racewear Ver. 1/7 Scale Figure</t>
+  </si>
+  <si>
+    <t>Sentenced to Be a Hero: The Prison Records of Penal Hero Unit 9004 Patausche Kivia 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Fate/strange Fake Francesca Prelati 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>"Nijisanji" Makaino Ririmu illustrated by kei Mochizuki 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>SNK Bishoujo Kula Diamond -THE KING OF FIGHTERS XV- 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Umamusume Pretty Derby [Shiun no Yumemitori] Tokai Teio 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>OSHI WORKS SILENT HILL 2 Abstract Daddy 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Anime "Uma Musume Cinderella Gray" Tamamo Cross 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Cane Bunny Girl illustration by Tuzhate 1/7 Complete Figure Deluxe Edition</t>
+  </si>
+  <si>
+    <t>Cane Bunny Girl illustration by Tuzhate 1/7 Complete Figure</t>
   </si>
   <si>
     <t>GODDESS OF VICTORY: NIKKE Modernia - Second Affection 1/7 Complete Figure</t>
   </si>
   <si>
-    <t>GODDESS OF VICTORY: NIKKE Quency: Escape Queen 1/7 Complete Figure</t>
+    <t>[Bonus] Honkai: Star Rail Aventurine 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Umamusume Pretty Derby Hishi Miracle 1/7 Complete Figure</t>
   </si>
   <si>
     <t>Character Vocal Series 01 Hatsune Miku 15th Anniversary Ver. 1/7 Complete Figure</t>
@@ -94,40 +364,313 @@
     <t>Blue Archive Shiroko*Terror 1/7 Complete Figure</t>
   </si>
   <si>
+    <t>Atelier Yumia: The Alchemist of Memories &amp; the Envisioned Land Yumia Liessfeldt Swimsuit Ver. 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Eromanga Sensei Elf Yamada 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>How NOT to Summon a Demon Lord Omega Shera L. Greenwood -Wedding Dress- 1/7 Complete Figure</t>
+  </si>
+  <si>
+    <t>Satou Kuuki Original Character Eviltia 1/7 Complete Figure (Native Online Shop Exclusive)</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-161001-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-017765-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIG-MOE-0789-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-126188-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-026139-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-124252-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-171497-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=HOB-FIG-0390-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-151678-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-141897-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-015538-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-135523-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-134160-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-170427-R</t>
+  </si>
+  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181987</t>
   </si>
   <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-180677-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-182085</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-044287-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-037544-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-164942-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-190694</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-180385</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-175404</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181248</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-172221</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-022718-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-056128-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-174908</t>
+  </si>
+  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-171348</t>
   </si>
   <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181529</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-176220</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-047292-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181372</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-037350-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-185214-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-136456</t>
+  </si>
+  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-177201</t>
   </si>
   <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181372</t>
-  </si>
-  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-185231</t>
   </si>
   <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-182256</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-167690</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181373</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-188689</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-192661</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-164629-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-002887-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-185473-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-171577-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-184003-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-179186</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-180136</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-040115-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-021598-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-129257-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-043409-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-125049-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-046703-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-134967</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-152830</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-134389</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-170858</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-154014</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-051939-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-187442</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIG-MOE-5005-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-161172-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-184409</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIG-MOE-0204-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181648</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-185745-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-040074-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-186962-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-189359</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-125314-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-196044</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181818</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-195698</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-189641</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-194344-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-190124-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-191898-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-186829-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-191826-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-183456</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-187441</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-151959-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-039656-R</t>
+  </si>
+  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-193741</t>
   </si>
   <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-188732</t>
-  </si>
-  <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-195698</t>
-  </si>
-  <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-181818</t>
-  </si>
-  <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-189641</t>
-  </si>
-  <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-183456</t>
-  </si>
-  <si>
-    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-187441</t>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-192157</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-198616</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-194191</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-199991</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-199777</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-196292</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-200050</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-196253</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-193066</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-193516</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-186973</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-186974</t>
   </si>
   <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-189651</t>
@@ -136,52 +679,334 @@
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-191826</t>
   </si>
   <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-187270</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-197290-R</t>
+  </si>
+  <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-190114</t>
   </si>
   <si>
     <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-190380</t>
   </si>
   <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-187842</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-041741-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-127576-R</t>
+  </si>
+  <si>
+    <t>https://www.amiami.com/eng/detail/?gcode=FIGURE-172627-R</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/234/FIGURE-161001.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/161/FIGURE-017765.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/093/FIG-MOE-0789.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/212/FIGURE-126188.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/164/FIGURE-026139.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/211/FIGURE-124252.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-171497.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/074/HOB-FIG-0390.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/231/FIGURE-151678.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/222/FIGURE-141897.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/154/FIGURE-015538.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/221/FIGURE-135523.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/214/FIGURE-134160.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/242/FIGURE-170427.jpg</t>
+  </si>
+  <si>
     <t>https://img.amiami.com/images/product/main/251/FIGURE-181987.jpg</t>
   </si>
   <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-180677.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-182085.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/191/FIGURE-044287.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/181/FIGURE-037544.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/241/FIGURE-164942.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-190694.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-180385.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/243/FIGURE-175404.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-181248.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/242/FIGURE-172221.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/163/FIGURE-022718.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/201/FIGURE-056128.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/243/FIGURE-174908.jpg</t>
+  </si>
+  <si>
     <t>https://img.amiami.com/images/product/main/242/FIGURE-171348.jpg</t>
   </si>
   <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-181529.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/243/FIGURE-176220.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/192/FIGURE-047292.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-181372.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/181/FIGURE-037350.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-185214.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/221/FIGURE-136456.jpg</t>
+  </si>
+  <si>
     <t>https://img.amiami.com/images/product/main/244/FIGURE-177201.jpg</t>
   </si>
   <si>
-    <t>https://img.amiami.com/images/product/main/251/FIGURE-181372.jpg</t>
-  </si>
-  <si>
     <t>https://img.amiami.com/images/product/main/252/FIGURE-185231.jpg</t>
   </si>
   <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-182256.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/241/FIGURE-167690.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-181373.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-188689.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-192661.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/241/FIGURE-164629.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/142/FIGURE-002887.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-185473.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/242/FIGURE-171577.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-184003.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-179186.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/244/FIGURE-180136.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/182/FIGURE-040115.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/172/FIGURE-021598.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/213/FIGURE-129257.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/184/FIGURE-043409.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/211/FIGURE-125049.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/191/FIGURE-046703.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/214/FIGURE-134967.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/231/FIGURE-152830.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/214/FIGURE-134389.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/242/FIGURE-170858.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/232/FIGURE-154014.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/193/FIGURE-051939.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-187442.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/114/FIG-MOE-5005.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/234/FIGURE-161172.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-184409.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/0809/FIG-MOE-0204.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-181648.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-185745.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/182/FIGURE-040074.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-186962.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-189359.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/212/FIGURE-125314.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-196044.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-181818.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-195698.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-189641.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-194344.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-190124.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-191898.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-186829.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-191826.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/251/FIGURE-183456.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/253/FIGURE-187441.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/231/FIGURE-151959.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/182/FIGURE-039656.jpg</t>
+  </si>
+  <si>
     <t>https://img.amiami.com/images/product/main/254/FIGURE-193741.jpg</t>
   </si>
   <si>
-    <t>https://img.amiami.com/images/product/main/253/FIGURE-188732.jpg</t>
-  </si>
-  <si>
-    <t>https://img.amiami.com/images/product/main/254/FIGURE-195698.jpg</t>
-  </si>
-  <si>
-    <t>https://img.amiami.com/images/product/main/251/FIGURE-181818.jpg</t>
-  </si>
-  <si>
-    <t>https://img.amiami.com/images/product/main/253/FIGURE-189641.jpg</t>
-  </si>
-  <si>
-    <t>https://img.amiami.com/images/product/main/251/FIGURE-183456.jpg</t>
-  </si>
-  <si>
-    <t>https://img.amiami.com/images/product/main/253/FIGURE-187441.jpg</t>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-192157.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/261/FIGURE-198616.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-194191.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/261/FIGURE-199991.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/261/FIGURE-199777.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-196292.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/262/FIGURE-200050.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-196253.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-193066.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/254/FIGURE-193516.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-186973.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-186974.jpg</t>
   </si>
   <si>
     <t>https://img.amiami.com/images/product/main/253/FIGURE-189651.jpg</t>
   </si>
   <si>
-    <t>https://img.amiami.com/images/product/main/253/FIGURE-191826.jpg</t>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-187270.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/261/FIGURE-197290.jpg</t>
   </si>
   <si>
     <t>https://img.amiami.com/images/product/main/253/FIGURE-190114.jpg</t>
@@ -190,25 +1015,202 @@
     <t>https://img.amiami.com/images/product/main/253/FIGURE-190380.jpg</t>
   </si>
   <si>
-    <t>14,280 JPY</t>
+    <t>https://img.amiami.com/images/product/main/252/FIGURE-187842.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/183/FIGURE-041741.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/212/FIGURE-127576.jpg</t>
+  </si>
+  <si>
+    <t>https://img.amiami.com/images/product/main/243/FIGURE-172627.jpg</t>
+  </si>
+  <si>
+    <t>7,980 JPY</t>
+  </si>
+  <si>
+    <t>5,980 JPY</t>
+  </si>
+  <si>
+    <t>2,450 JPY</t>
+  </si>
+  <si>
+    <t>6,380 JPY</t>
+  </si>
+  <si>
+    <t>8,720 JPY</t>
+  </si>
+  <si>
+    <t>13,480 JPY</t>
+  </si>
+  <si>
+    <t>4,980 JPY</t>
+  </si>
+  <si>
+    <t>8,080 JPY</t>
+  </si>
+  <si>
+    <t>9,980 JPY</t>
+  </si>
+  <si>
+    <t>5,580 JPY</t>
+  </si>
+  <si>
+    <t>9,880 JPY</t>
+  </si>
+  <si>
+    <t>11,680 JPY</t>
+  </si>
+  <si>
+    <t>15,280 JPY</t>
+  </si>
+  <si>
+    <t>11,250 JPY</t>
+  </si>
+  <si>
+    <t>12,980 JPY</t>
+  </si>
+  <si>
+    <t>7,480 JPY</t>
+  </si>
+  <si>
+    <t>16,980 JPY</t>
+  </si>
+  <si>
+    <t>15,980 JPY</t>
+  </si>
+  <si>
+    <t>14,520 JPY</t>
+  </si>
+  <si>
+    <t>17,160 JPY</t>
+  </si>
+  <si>
+    <t>10,206 JPY</t>
+  </si>
+  <si>
+    <t>9,580 JPY</t>
+  </si>
+  <si>
+    <t>25,980 JPY</t>
   </si>
   <si>
     <t>25,600 JPY</t>
   </si>
   <si>
-    <t>5,980 JPY</t>
+    <t>16,802 JPY</t>
+  </si>
+  <si>
+    <t>14,300 JPY</t>
   </si>
   <si>
     <t>19,980 JPY</t>
   </si>
   <si>
+    <t>13,980 JPY</t>
+  </si>
+  <si>
+    <t>17,550 JPY</t>
+  </si>
+  <si>
+    <t>21,800 JPY</t>
+  </si>
+  <si>
+    <t>6,468 JPY</t>
+  </si>
+  <si>
     <t>16,660 JPY</t>
   </si>
   <si>
-    <t>23,010 JPY</t>
-  </si>
-  <si>
-    <t>34,650 JPY</t>
+    <t>17,640 JPY</t>
+  </si>
+  <si>
+    <t>19,250 JPY</t>
+  </si>
+  <si>
+    <t>16,800 JPY</t>
+  </si>
+  <si>
+    <t>6,930 JPY</t>
+  </si>
+  <si>
+    <t>11,935 JPY</t>
+  </si>
+  <si>
+    <t>10,780 JPY</t>
+  </si>
+  <si>
+    <t>6,980 JPY</t>
+  </si>
+  <si>
+    <t>18,880 JPY</t>
+  </si>
+  <si>
+    <t>21,280 JPY</t>
+  </si>
+  <si>
+    <t>17,980 JPY</t>
+  </si>
+  <si>
+    <t>17,280 JPY</t>
+  </si>
+  <si>
+    <t>10,440 JPY</t>
+  </si>
+  <si>
+    <t>11,390 JPY</t>
+  </si>
+  <si>
+    <t>12,580 JPY</t>
+  </si>
+  <si>
+    <t>19,820 JPY</t>
+  </si>
+  <si>
+    <t>43,200 JPY</t>
+  </si>
+  <si>
+    <t>17,510 JPY</t>
+  </si>
+  <si>
+    <t>15,840 JPY</t>
+  </si>
+  <si>
+    <t>17,600 JPY</t>
+  </si>
+  <si>
+    <t>11,590 JPY</t>
+  </si>
+  <si>
+    <t>18,010 JPY</t>
+  </si>
+  <si>
+    <t>16,780 JPY</t>
+  </si>
+  <si>
+    <t>22,780 JPY</t>
+  </si>
+  <si>
+    <t>7,360 JPY</t>
+  </si>
+  <si>
+    <t>24,000 JPY</t>
+  </si>
+  <si>
+    <t>20,980 JPY</t>
+  </si>
+  <si>
+    <t>12,280 JPY</t>
+  </si>
+  <si>
+    <t>19,350 JPY</t>
+  </si>
+  <si>
+    <t>15,480 JPY</t>
+  </si>
+  <si>
+    <t>24,250 JPY</t>
   </si>
   <si>
     <t>20,790 JPY</t>
@@ -217,103 +1219,514 @@
     <t>19,800 JPY</t>
   </si>
   <si>
+    <t>23,980 JPY</t>
+  </si>
+  <si>
+    <t>23,660 JPY</t>
+  </si>
+  <si>
+    <t>20,780 JPY</t>
+  </si>
+  <si>
     <t>23,320 JPY</t>
   </si>
   <si>
     <t>21,000 JPY</t>
   </si>
   <si>
+    <t>16,480 JPY</t>
+  </si>
+  <si>
+    <t>26,120 JPY</t>
+  </si>
+  <si>
+    <t>36,360 JPY</t>
+  </si>
+  <si>
+    <t>30,300 JPY</t>
+  </si>
+  <si>
+    <t>24,030 JPY</t>
+  </si>
+  <si>
+    <t>18,810 JPY</t>
+  </si>
+  <si>
+    <t>25,080 JPY</t>
+  </si>
+  <si>
+    <t>8,360 JPY</t>
+  </si>
+  <si>
+    <t>25,720 JPY</t>
+  </si>
+  <si>
+    <t>24,500 JPY</t>
+  </si>
+  <si>
+    <t>22,400 JPY</t>
+  </si>
+  <si>
     <t>25,996 JPY</t>
   </si>
   <si>
     <t>22,100 JPY</t>
   </si>
   <si>
+    <t>39,670 JPY</t>
+  </si>
+  <si>
+    <t>21,580 JPY</t>
+  </si>
+  <si>
     <t>42,895 JPY</t>
   </si>
   <si>
     <t>23,562 JPY</t>
   </si>
   <si>
+    <t>23,780 JPY</t>
+  </si>
+  <si>
+    <t>19,780 JPY</t>
+  </si>
+  <si>
+    <t>27,280 JPY</t>
+  </si>
+  <si>
+    <t>18,480 JPY</t>
+  </si>
+  <si>
+    <t>16,500 JPY</t>
+  </si>
+  <si>
+    <t>16,280 JPY</t>
+  </si>
+  <si>
+    <t>20,680 JPY</t>
+  </si>
+  <si>
+    <t>29,700 JPY</t>
+  </si>
+  <si>
+    <t>17,380 JPY</t>
+  </si>
+  <si>
+    <t>19,900 JPY</t>
+  </si>
+  <si>
+    <t>18,700 JPY</t>
+  </si>
+  <si>
+    <t>15,278 JPY</t>
+  </si>
+  <si>
+    <t>22,000 JPY</t>
+  </si>
+  <si>
     <t>28,500 JPY</t>
   </si>
   <si>
+    <t>22,700 JPY</t>
+  </si>
+  <si>
+    <t>12,731 JPY</t>
+  </si>
+  <si>
+    <t>28,600 JPY</t>
+  </si>
+  <si>
+    <t>26,800 JPY</t>
+  </si>
+  <si>
+    <t>24,200 JPY</t>
+  </si>
+  <si>
+    <t>16,200 JPY</t>
+  </si>
+  <si>
+    <t>15,180 JPY</t>
+  </si>
+  <si>
+    <t>17,800 JPY</t>
+  </si>
+  <si>
+    <t>40,590 JPY</t>
+  </si>
+  <si>
     <t>39,600 JPY</t>
   </si>
   <si>
+    <t>25,850 JPY</t>
+  </si>
+  <si>
+    <t>30,580 JPY</t>
+  </si>
+  <si>
+    <t>20,166 JPY</t>
+  </si>
+  <si>
+    <t>25,300 JPY</t>
+  </si>
+  <si>
+    <t>31,350 JPY</t>
+  </si>
+  <si>
     <t>9,240 JPY</t>
   </si>
   <si>
-    <t>30,580 JPY</t>
-  </si>
-  <si>
     <t>23,800 JPY</t>
   </si>
   <si>
+    <t>25,200 JPY</t>
+  </si>
+  <si>
     <t>27,500 JPY</t>
   </si>
   <si>
-    <t>38,900 JPY</t>
+    <t>9,900 JPY</t>
+  </si>
+  <si>
+    <t>17,050 JPY</t>
+  </si>
+  <si>
+    <t>15,400 JPY</t>
+  </si>
+  <si>
+    <t>9,952 JPY</t>
+  </si>
+  <si>
+    <t>26,400 JPY</t>
+  </si>
+  <si>
+    <t>25,000 JPY</t>
+  </si>
+  <si>
+    <t>23,650 JPY</t>
+  </si>
+  <si>
+    <t>14,056 JPY</t>
+  </si>
+  <si>
+    <t>13,241 JPY</t>
+  </si>
+  <si>
+    <t>20,350 JPY</t>
+  </si>
+  <si>
+    <t>14,850 JPY</t>
+  </si>
+  <si>
+    <t>16,093 JPY</t>
+  </si>
+  <si>
+    <t>54,010 JPY</t>
+  </si>
+  <si>
+    <t>21,890 JPY</t>
+  </si>
+  <si>
+    <t>9,680 JPY</t>
+  </si>
+  <si>
+    <t>8,580 JPY</t>
+  </si>
+  <si>
+    <t>27,800 JPY</t>
+  </si>
+  <si>
+    <t>24,090 JPY</t>
+  </si>
+  <si>
+    <t>14,080 JPY</t>
+  </si>
+  <si>
+    <t>26,950 JPY</t>
   </si>
   <si>
     <t>23,100 JPY</t>
   </si>
   <si>
-    <t>22,000 JPY</t>
-  </si>
-  <si>
-    <t>25,080 JPY</t>
+    <t>25,801 JPY</t>
+  </si>
+  <si>
+    <t>22,600 JPY</t>
   </si>
   <si>
     <t>22,440 JPY</t>
   </si>
   <si>
-    <t>26,800 JPY</t>
-  </si>
-  <si>
-    <t>22,600 JPY</t>
+    <t>38,280 JPY</t>
+  </si>
+  <si>
+    <t>31,900 JPY</t>
+  </si>
+  <si>
+    <t>8,800 JPY</t>
+  </si>
+  <si>
+    <t>40,480 JPY</t>
   </si>
   <si>
     <t>43,329 JPY</t>
   </si>
   <si>
-    <t>49.89%</t>
+    <t>70.75%</t>
+  </si>
+  <si>
+    <t>67.64%</t>
+  </si>
+  <si>
+    <t>67.25%</t>
+  </si>
+  <si>
+    <t>61.33%</t>
+  </si>
+  <si>
+    <t>60.81%</t>
+  </si>
+  <si>
+    <t>57.83%</t>
+  </si>
+  <si>
+    <t>54.61%</t>
+  </si>
+  <si>
+    <t>53.8%</t>
+  </si>
+  <si>
+    <t>53.51%</t>
+  </si>
+  <si>
+    <t>49.85%</t>
+  </si>
+  <si>
+    <t>48.24%</t>
+  </si>
+  <si>
+    <t>47.17%</t>
+  </si>
+  <si>
+    <t>47.11%</t>
+  </si>
+  <si>
+    <t>46.91%</t>
+  </si>
+  <si>
+    <t>46.39%</t>
+  </si>
+  <si>
+    <t>43.18%</t>
+  </si>
+  <si>
+    <t>42.82%</t>
+  </si>
+  <si>
+    <t>42.58%</t>
+  </si>
+  <si>
+    <t>41.25%</t>
+  </si>
+  <si>
+    <t>41.01%</t>
+  </si>
+  <si>
+    <t>40.63%</t>
+  </si>
+  <si>
+    <t>40.37%</t>
+  </si>
+  <si>
+    <t>40.0%</t>
+  </si>
+  <si>
+    <t>37.0%</t>
+  </si>
+  <si>
+    <t>36.89%</t>
+  </si>
+  <si>
+    <t>36.8%</t>
+  </si>
+  <si>
+    <t>35.99%</t>
   </si>
   <si>
     <t>35.35%</t>
   </si>
   <si>
-    <t>35.28%</t>
+    <t>35.0%</t>
+  </si>
+  <si>
+    <t>34.91%</t>
   </si>
   <si>
     <t>34.66%</t>
   </si>
   <si>
+    <t>30.68%</t>
+  </si>
+  <si>
+    <t>30.63%</t>
+  </si>
+  <si>
+    <t>30.46%</t>
+  </si>
+  <si>
     <t>30.0%</t>
   </si>
   <si>
-    <t>16.33%</t>
+    <t>29.86%</t>
+  </si>
+  <si>
+    <t>28.48%</t>
+  </si>
+  <si>
+    <t>28.35%</t>
+  </si>
+  <si>
+    <t>28.08%</t>
+  </si>
+  <si>
+    <t>27.35%</t>
+  </si>
+  <si>
+    <t>26.93%</t>
+  </si>
+  <si>
+    <t>25.73%</t>
+  </si>
+  <si>
+    <t>25.38%</t>
+  </si>
+  <si>
+    <t>24.91%</t>
+  </si>
+  <si>
+    <t>23.3%</t>
+  </si>
+  <si>
+    <t>23.11%</t>
+  </si>
+  <si>
+    <t>21.83%</t>
+  </si>
+  <si>
+    <t>20.97%</t>
+  </si>
+  <si>
+    <t>20.01%</t>
+  </si>
+  <si>
+    <t>20.0%</t>
+  </si>
+  <si>
+    <t>18.95%</t>
+  </si>
+  <si>
+    <t>18.14%</t>
+  </si>
+  <si>
+    <t>17.56%</t>
+  </si>
+  <si>
+    <t>15.25%</t>
+  </si>
+  <si>
+    <t>15.0%</t>
+  </si>
+  <si>
+    <t>14.22%</t>
+  </si>
+  <si>
+    <t>13.67%</t>
+  </si>
+  <si>
+    <t>12.91%</t>
+  </si>
+  <si>
+    <t>12.78%</t>
+  </si>
+  <si>
+    <t>12.53%</t>
+  </si>
+  <si>
+    <t>11.24%</t>
   </si>
   <si>
     <t>10.93%</t>
   </si>
   <si>
+    <t>10.02%</t>
+  </si>
+  <si>
     <t>10.0%</t>
   </si>
   <si>
+    <t>9.19%</t>
+  </si>
+  <si>
+    <t>9.17%</t>
+  </si>
+  <si>
+    <t>9.16%</t>
+  </si>
+  <si>
+    <t>8.3%</t>
+  </si>
+  <si>
+    <t>8.05%</t>
+  </si>
+  <si>
     <t>7.02%</t>
   </si>
   <si>
     <t>6.42%</t>
   </si>
   <si>
+    <t>5.55%</t>
+  </si>
+  <si>
+    <t>5.18%</t>
+  </si>
+  <si>
+    <t>5.02%</t>
+  </si>
+  <si>
+    <t>5.0%</t>
+  </si>
+  <si>
+    <t>4.03%</t>
+  </si>
+  <si>
+    <t>3.16%</t>
+  </si>
+  <si>
+    <t>3.03%</t>
+  </si>
+  <si>
     <t>3.0%</t>
   </si>
   <si>
     <t>2.21%</t>
   </si>
   <si>
+    <t>2.0%</t>
+  </si>
+  <si>
+    <t>1.91%</t>
+  </si>
+  <si>
     <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.83%</t>
+  </si>
+  <si>
+    <t>0.71%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
   </si>
 </sst>
 </file>
@@ -687,12 +2100,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="50.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="56.7109375" customWidth="1"/>
+    <col min="3" max="3" width="58.7109375" customWidth="1"/>
     <col min="4" max="4" width="66.7109375" customWidth="1"/>
     <col min="5" max="5" width="18.7109375" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" customWidth="1"/>
@@ -727,22 +2140,22 @@
         <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>41</v>
+        <v>228</v>
       </c>
       <c r="E2" t="s">
-        <v>57</v>
+        <v>336</v>
       </c>
       <c r="F2" t="s">
-        <v>72</v>
+        <v>424</v>
       </c>
       <c r="G2" t="s">
-        <v>86</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -750,22 +2163,22 @@
         <v>7</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>120</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>229</v>
       </c>
       <c r="E3" t="s">
-        <v>58</v>
+        <v>337</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>425</v>
       </c>
       <c r="G3" t="s">
-        <v>87</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -773,22 +2186,22 @@
         <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>27</v>
+        <v>121</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>43</v>
+        <v>230</v>
       </c>
       <c r="E4" t="s">
-        <v>59</v>
+        <v>338</v>
       </c>
       <c r="F4" t="s">
-        <v>74</v>
+        <v>351</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -796,22 +2209,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>28</v>
+        <v>122</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>44</v>
+        <v>231</v>
       </c>
       <c r="E5" t="s">
-        <v>60</v>
+        <v>339</v>
       </c>
       <c r="F5" t="s">
-        <v>75</v>
+        <v>426</v>
       </c>
       <c r="G5" t="s">
-        <v>89</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -819,229 +2232,229 @@
         <v>7</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>45</v>
+        <v>232</v>
       </c>
       <c r="E6" t="s">
-        <v>61</v>
+        <v>339</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>427</v>
       </c>
       <c r="G6" t="s">
-        <v>90</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>30</v>
+        <v>124</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>46</v>
+        <v>233</v>
       </c>
       <c r="E7" t="s">
-        <v>62</v>
+        <v>340</v>
       </c>
       <c r="F7" t="s">
-        <v>77</v>
+        <v>428</v>
       </c>
       <c r="G7" t="s">
-        <v>91</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>125</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>47</v>
+        <v>234</v>
       </c>
       <c r="E8" t="s">
-        <v>63</v>
+        <v>341</v>
       </c>
       <c r="F8" t="s">
-        <v>78</v>
+        <v>429</v>
       </c>
       <c r="G8" t="s">
-        <v>92</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>48</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>342</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>373</v>
       </c>
       <c r="G9" t="s">
-        <v>93</v>
+        <v>491</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>33</v>
+        <v>127</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>49</v>
+        <v>236</v>
       </c>
       <c r="E10" t="s">
-        <v>64</v>
+        <v>343</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>430</v>
       </c>
       <c r="G10" t="s">
-        <v>93</v>
+        <v>492</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>34</v>
+        <v>128</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>50</v>
+        <v>237</v>
       </c>
       <c r="E11" t="s">
-        <v>65</v>
+        <v>344</v>
       </c>
       <c r="F11" t="s">
-        <v>80</v>
+        <v>431</v>
       </c>
       <c r="G11" t="s">
-        <v>93</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>51</v>
+        <v>238</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>345</v>
       </c>
       <c r="F12" t="s">
-        <v>81</v>
+        <v>373</v>
       </c>
       <c r="G12" t="s">
-        <v>94</v>
+        <v>494</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>52</v>
+        <v>239</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>346</v>
       </c>
       <c r="F13" t="s">
-        <v>82</v>
+        <v>432</v>
       </c>
       <c r="G13" t="s">
-        <v>95</v>
+        <v>495</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>37</v>
+        <v>131</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
+        <v>240</v>
       </c>
       <c r="E14" t="s">
-        <v>68</v>
+        <v>343</v>
       </c>
       <c r="F14" t="s">
-        <v>83</v>
+        <v>433</v>
       </c>
       <c r="G14" t="s">
-        <v>96</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>38</v>
+        <v>132</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>54</v>
+        <v>241</v>
       </c>
       <c r="E15" t="s">
-        <v>69</v>
+        <v>347</v>
       </c>
       <c r="F15" t="s">
-        <v>84</v>
+        <v>434</v>
       </c>
       <c r="G15" t="s">
-        <v>97</v>
+        <v>497</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -1049,49 +2462,2188 @@
         <v>8</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>39</v>
+        <v>133</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>55</v>
+        <v>242</v>
       </c>
       <c r="E16" t="s">
-        <v>70</v>
+        <v>348</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>435</v>
       </c>
       <c r="G16" t="s">
-        <v>98</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E17" t="s">
+        <v>349</v>
+      </c>
+      <c r="F17" t="s">
+        <v>399</v>
+      </c>
+      <c r="G17" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="3" t="s">
+      <c r="B18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="E18" t="s">
+        <v>350</v>
+      </c>
+      <c r="F18" t="s">
+        <v>436</v>
+      </c>
+      <c r="G18" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E19" t="s">
+        <v>344</v>
+      </c>
+      <c r="F19" t="s">
+        <v>430</v>
+      </c>
+      <c r="G19" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="E20" t="s">
+        <v>351</v>
+      </c>
+      <c r="F20" t="s">
+        <v>437</v>
+      </c>
+      <c r="G20" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E21" t="s">
+        <v>347</v>
+      </c>
+      <c r="F21" t="s">
+        <v>399</v>
+      </c>
+      <c r="G21" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E22" t="s">
+        <v>352</v>
+      </c>
+      <c r="F22" t="s">
+        <v>438</v>
+      </c>
+      <c r="G22" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="E23" t="s">
+        <v>353</v>
+      </c>
+      <c r="F23" t="s">
+        <v>439</v>
+      </c>
+      <c r="G23" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="E24" t="s">
+        <v>354</v>
+      </c>
+      <c r="F24" t="s">
+        <v>440</v>
+      </c>
+      <c r="G24" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="E25" t="s">
+        <v>355</v>
+      </c>
+      <c r="F25" t="s">
+        <v>438</v>
+      </c>
+      <c r="G25" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="E26" t="s">
+        <v>356</v>
+      </c>
+      <c r="F26" t="s">
+        <v>441</v>
+      </c>
+      <c r="G26" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="E27" t="s">
+        <v>357</v>
+      </c>
+      <c r="F27" t="s">
+        <v>442</v>
+      </c>
+      <c r="G27" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E28" t="s">
+        <v>349</v>
+      </c>
+      <c r="F28" t="s">
+        <v>443</v>
+      </c>
+      <c r="G28" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="E29" t="s">
+        <v>358</v>
+      </c>
+      <c r="F29" t="s">
+        <v>444</v>
+      </c>
+      <c r="G29" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="E30" t="s">
+        <v>359</v>
+      </c>
+      <c r="F30" t="s">
+        <v>445</v>
+      </c>
+      <c r="G30" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" t="s">
+        <v>8</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="C31" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="E31" t="s">
+        <v>360</v>
+      </c>
+      <c r="F31" t="s">
+        <v>446</v>
+      </c>
+      <c r="G31" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" t="s">
+        <v>8</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="E32" t="s">
+        <v>361</v>
+      </c>
+      <c r="F32" t="s">
+        <v>434</v>
+      </c>
+      <c r="G32" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" t="s">
+        <v>7</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="E33" t="s">
+        <v>346</v>
+      </c>
+      <c r="F33" t="s">
+        <v>442</v>
+      </c>
+      <c r="G33" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" t="s">
+        <v>8</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E34" t="s">
+        <v>362</v>
+      </c>
+      <c r="F34" t="s">
+        <v>447</v>
+      </c>
+      <c r="G34" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E35" t="s">
+        <v>363</v>
+      </c>
+      <c r="F35" t="s">
+        <v>448</v>
+      </c>
+      <c r="G35" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="E36" t="s">
+        <v>364</v>
+      </c>
+      <c r="F36" t="s">
+        <v>449</v>
+      </c>
+      <c r="G36" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" t="s">
+        <v>8</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="E37" t="s">
+        <v>365</v>
+      </c>
+      <c r="F37" t="s">
+        <v>450</v>
+      </c>
+      <c r="G37" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" t="s">
+        <v>8</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="E38" t="s">
+        <v>366</v>
+      </c>
+      <c r="F38" t="s">
+        <v>451</v>
+      </c>
+      <c r="G38" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="E39" t="s">
+        <v>367</v>
+      </c>
+      <c r="F39" t="s">
+        <v>452</v>
+      </c>
+      <c r="G39" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="E40" t="s">
+        <v>368</v>
+      </c>
+      <c r="F40" t="s">
+        <v>453</v>
+      </c>
+      <c r="G40" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="E41" t="s">
+        <v>369</v>
+      </c>
+      <c r="F41" t="s">
+        <v>454</v>
+      </c>
+      <c r="G41" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" t="s">
+        <v>8</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="E42" t="s">
+        <v>370</v>
+      </c>
+      <c r="F42" t="s">
+        <v>392</v>
+      </c>
+      <c r="G42" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="E43" t="s">
+        <v>371</v>
+      </c>
+      <c r="F43" t="s">
+        <v>455</v>
+      </c>
+      <c r="G43" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E44" t="s">
+        <v>372</v>
+      </c>
+      <c r="F44" t="s">
+        <v>456</v>
+      </c>
+      <c r="G44" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="E45" t="s">
+        <v>373</v>
+      </c>
+      <c r="F45" t="s">
+        <v>457</v>
+      </c>
+      <c r="G45" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="E46" t="s">
+        <v>374</v>
+      </c>
+      <c r="F46" t="s">
+        <v>458</v>
+      </c>
+      <c r="G46" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E17" t="s">
+      <c r="C47" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E47" t="s">
+        <v>375</v>
+      </c>
+      <c r="F47" t="s">
+        <v>459</v>
+      </c>
+      <c r="G47" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="E48" t="s">
+        <v>376</v>
+      </c>
+      <c r="F48" t="s">
+        <v>429</v>
+      </c>
+      <c r="G48" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="E49" t="s">
+        <v>377</v>
+      </c>
+      <c r="F49" t="s">
+        <v>460</v>
+      </c>
+      <c r="G49" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>8</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E50" t="s">
+        <v>362</v>
+      </c>
+      <c r="F50" t="s">
+        <v>454</v>
+      </c>
+      <c r="G50" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>8</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="E51" t="s">
+        <v>378</v>
+      </c>
+      <c r="F51" t="s">
+        <v>461</v>
+      </c>
+      <c r="G51" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="E52" t="s">
+        <v>379</v>
+      </c>
+      <c r="F52" t="s">
+        <v>462</v>
+      </c>
+      <c r="G52" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="E53" t="s">
+        <v>346</v>
+      </c>
+      <c r="F53" t="s">
+        <v>463</v>
+      </c>
+      <c r="G53" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E54" t="s">
+        <v>348</v>
+      </c>
+      <c r="F54" t="s">
+        <v>464</v>
+      </c>
+      <c r="G54" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="E55" t="s">
+        <v>380</v>
+      </c>
+      <c r="F55" t="s">
+        <v>465</v>
+      </c>
+      <c r="G55" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="E56" t="s">
+        <v>344</v>
+      </c>
+      <c r="F56" t="s">
+        <v>350</v>
+      </c>
+      <c r="G56" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="E57" t="s">
+        <v>381</v>
+      </c>
+      <c r="F57" t="s">
+        <v>466</v>
+      </c>
+      <c r="G57" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="E58" t="s">
+        <v>382</v>
+      </c>
+      <c r="F58" t="s">
+        <v>411</v>
+      </c>
+      <c r="G58" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" t="s">
+        <v>9</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="E59" t="s">
+        <v>383</v>
+      </c>
+      <c r="F59" t="s">
+        <v>467</v>
+      </c>
+      <c r="G59" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E60" t="s">
+        <v>384</v>
+      </c>
+      <c r="F60" t="s">
+        <v>468</v>
+      </c>
+      <c r="G60" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="E61" t="s">
+        <v>385</v>
+      </c>
+      <c r="F61" t="s">
+        <v>399</v>
+      </c>
+      <c r="G61" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" t="s">
+        <v>9</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="F17" t="s">
+      <c r="C62" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E62" t="s">
+        <v>386</v>
+      </c>
+      <c r="F62" t="s">
+        <v>434</v>
+      </c>
+      <c r="G62" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D63" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="E63" t="s">
+        <v>387</v>
+      </c>
+      <c r="F63" t="s">
+        <v>361</v>
+      </c>
+      <c r="G63" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64" t="s">
+        <v>9</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="E64" t="s">
+        <v>388</v>
+      </c>
+      <c r="F64" t="s">
+        <v>434</v>
+      </c>
+      <c r="G64" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E65" t="s">
+        <v>336</v>
+      </c>
+      <c r="F65" t="s">
+        <v>469</v>
+      </c>
+      <c r="G65" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E66" t="s">
+        <v>389</v>
+      </c>
+      <c r="F66" t="s">
+        <v>399</v>
+      </c>
+      <c r="G66" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67" t="s">
+        <v>9</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G17" t="s">
+      <c r="C67" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E67" t="s">
+        <v>390</v>
+      </c>
+      <c r="F67" t="s">
+        <v>439</v>
+      </c>
+      <c r="G67" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68" t="s">
+        <v>7</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D68" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="E68" t="s">
+        <v>391</v>
+      </c>
+      <c r="F68" t="s">
+        <v>470</v>
+      </c>
+      <c r="G68" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D69" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="E69" t="s">
+        <v>392</v>
+      </c>
+      <c r="F69" t="s">
+        <v>471</v>
+      </c>
+      <c r="G69" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70" t="s">
+        <v>7</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="E70" t="s">
+        <v>393</v>
+      </c>
+      <c r="F70" t="s">
+        <v>472</v>
+      </c>
+      <c r="G70" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71" t="s">
+        <v>7</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D71" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="E71" t="s">
+        <v>394</v>
+      </c>
+      <c r="F71" t="s">
+        <v>473</v>
+      </c>
+      <c r="G71" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72" t="s">
+        <v>7</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E72" t="s">
+        <v>358</v>
+      </c>
+      <c r="F72" t="s">
+        <v>429</v>
+      </c>
+      <c r="G72" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D73" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="E73" t="s">
+        <v>395</v>
+      </c>
+      <c r="F73" t="s">
+        <v>365</v>
+      </c>
+      <c r="G73" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74" t="s">
+        <v>7</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="E74" t="s">
+        <v>396</v>
+      </c>
+      <c r="F74" t="s">
+        <v>430</v>
+      </c>
+      <c r="G74" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D75" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E75" t="s">
+        <v>397</v>
+      </c>
+      <c r="F75" t="s">
+        <v>474</v>
+      </c>
+      <c r="G75" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7">
+      <c r="A76" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E76" t="s">
+        <v>398</v>
+      </c>
+      <c r="F76" t="s">
+        <v>475</v>
+      </c>
+      <c r="G76" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7">
+      <c r="A77" t="s">
+        <v>9</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="E77" t="s">
+        <v>398</v>
+      </c>
+      <c r="F77" t="s">
+        <v>475</v>
+      </c>
+      <c r="G77" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7">
+      <c r="A78" t="s">
+        <v>9</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D78" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="E78" t="s">
+        <v>399</v>
+      </c>
+      <c r="F78" t="s">
+        <v>434</v>
+      </c>
+      <c r="G78" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7">
+      <c r="A79" t="s">
+        <v>7</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="D79" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E79" t="s">
+        <v>377</v>
+      </c>
+      <c r="F79" t="s">
+        <v>399</v>
+      </c>
+      <c r="G79" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7">
+      <c r="A80" t="s">
+        <v>7</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="E80" t="s">
+        <v>400</v>
+      </c>
+      <c r="F80" t="s">
+        <v>459</v>
+      </c>
+      <c r="G80" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7">
+      <c r="A81" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E81" t="s">
+        <v>358</v>
+      </c>
+      <c r="F81" t="s">
+        <v>438</v>
+      </c>
+      <c r="G81" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7">
+      <c r="A82" t="s">
+        <v>7</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="E82" t="s">
+        <v>401</v>
+      </c>
+      <c r="F82" t="s">
+        <v>476</v>
+      </c>
+      <c r="G82" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7">
+      <c r="A83" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E83" t="s">
+        <v>402</v>
+      </c>
+      <c r="F83" t="s">
+        <v>477</v>
+      </c>
+      <c r="G83" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7">
+      <c r="A84" t="s">
+        <v>9</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="E84" t="s">
+        <v>403</v>
+      </c>
+      <c r="F84" t="s">
+        <v>411</v>
+      </c>
+      <c r="G84" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7">
+      <c r="A85" t="s">
+        <v>9</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E85" t="s">
+        <v>404</v>
+      </c>
+      <c r="F85" t="s">
+        <v>478</v>
+      </c>
+      <c r="G85" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7">
+      <c r="A86" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E86" t="s">
+        <v>402</v>
+      </c>
+      <c r="F86" t="s">
+        <v>434</v>
+      </c>
+      <c r="G86" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7">
+      <c r="A87" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="E87" t="s">
+        <v>405</v>
+      </c>
+      <c r="F87" t="s">
+        <v>430</v>
+      </c>
+      <c r="G87" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7">
+      <c r="A88" t="s">
+        <v>9</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E88" t="s">
+        <v>406</v>
+      </c>
+      <c r="F88" t="s">
+        <v>454</v>
+      </c>
+      <c r="G88" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7">
+      <c r="A89" t="s">
+        <v>9</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>98</v>
       </c>
+      <c r="C89" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="E89" t="s">
+        <v>406</v>
+      </c>
+      <c r="F89" t="s">
+        <v>454</v>
+      </c>
+      <c r="G89" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7">
+      <c r="A90" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="E90" t="s">
+        <v>407</v>
+      </c>
+      <c r="F90" t="s">
+        <v>479</v>
+      </c>
+      <c r="G90" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7">
+      <c r="A91" t="s">
+        <v>9</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="E91" t="s">
+        <v>406</v>
+      </c>
+      <c r="F91" t="s">
+        <v>454</v>
+      </c>
+      <c r="G91" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7">
+      <c r="A92" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="D92" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E92" t="s">
+        <v>408</v>
+      </c>
+      <c r="F92" t="s">
+        <v>480</v>
+      </c>
+      <c r="G92" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7">
+      <c r="A93" t="s">
+        <v>9</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E93" t="s">
+        <v>409</v>
+      </c>
+      <c r="F93" t="s">
+        <v>449</v>
+      </c>
+      <c r="G93" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7">
+      <c r="A94" t="s">
+        <v>9</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="D94" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="E94" t="s">
+        <v>410</v>
+      </c>
+      <c r="F94" t="s">
+        <v>399</v>
+      </c>
+      <c r="G94" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7">
+      <c r="A95" t="s">
+        <v>9</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="D95" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="E95" t="s">
+        <v>410</v>
+      </c>
+      <c r="F95" t="s">
+        <v>399</v>
+      </c>
+      <c r="G95" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7">
+      <c r="A96" t="s">
+        <v>9</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="D96" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="E96" t="s">
+        <v>411</v>
+      </c>
+      <c r="F96" t="s">
+        <v>459</v>
+      </c>
+      <c r="G96" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7">
+      <c r="A97" t="s">
+        <v>9</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="D97" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="E97" t="s">
+        <v>412</v>
+      </c>
+      <c r="F97" t="s">
+        <v>481</v>
+      </c>
+      <c r="G97" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7">
+      <c r="A98" t="s">
+        <v>9</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="D98" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E98" t="s">
+        <v>413</v>
+      </c>
+      <c r="F98" t="s">
+        <v>439</v>
+      </c>
+      <c r="G98" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7">
+      <c r="A99" t="s">
+        <v>9</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D99" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="E99" t="s">
+        <v>414</v>
+      </c>
+      <c r="F99" t="s">
+        <v>449</v>
+      </c>
+      <c r="G99" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7">
+      <c r="A100" t="s">
+        <v>9</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E100" t="s">
+        <v>415</v>
+      </c>
+      <c r="F100" t="s">
+        <v>475</v>
+      </c>
+      <c r="G100" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7">
+      <c r="A101" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="D101" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="E101" t="s">
+        <v>416</v>
+      </c>
+      <c r="F101" t="s">
+        <v>439</v>
+      </c>
+      <c r="G101" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7">
+      <c r="A102" t="s">
+        <v>9</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="D102" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="E102" t="s">
+        <v>417</v>
+      </c>
+      <c r="F102" t="s">
+        <v>477</v>
+      </c>
+      <c r="G102" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7">
+      <c r="A103" t="s">
+        <v>9</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D103" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="E103" t="s">
+        <v>418</v>
+      </c>
+      <c r="F103" t="s">
+        <v>482</v>
+      </c>
+      <c r="G103" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7">
+      <c r="A104" t="s">
+        <v>7</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D104" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="E104" t="s">
+        <v>419</v>
+      </c>
+      <c r="F104" t="s">
+        <v>434</v>
+      </c>
+      <c r="G104" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7">
+      <c r="A105" t="s">
+        <v>9</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="D105" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="E105" t="s">
+        <v>420</v>
+      </c>
+      <c r="F105" t="s">
+        <v>483</v>
+      </c>
+      <c r="G105" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7">
+      <c r="A106" t="s">
+        <v>9</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D106" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="E106" t="s">
+        <v>421</v>
+      </c>
+      <c r="F106" t="s">
+        <v>452</v>
+      </c>
+      <c r="G106" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7">
+      <c r="A107" t="s">
+        <v>9</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D107" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="E107" t="s">
+        <v>422</v>
+      </c>
+      <c r="F107" t="s">
+        <v>400</v>
+      </c>
+      <c r="G107" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7">
+      <c r="A108" t="s">
+        <v>7</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D108" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E108" t="s">
+        <v>363</v>
+      </c>
+      <c r="F108" t="s">
+        <v>473</v>
+      </c>
+      <c r="G108" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7">
+      <c r="A109" t="s">
+        <v>7</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D109" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="E109" t="s">
+        <v>423</v>
+      </c>
+      <c r="F109" t="s">
+        <v>399</v>
+      </c>
+      <c r="G109" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7">
+      <c r="A110" t="s">
+        <v>7</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="D110" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="E110" t="s">
+        <v>423</v>
+      </c>
+      <c r="F110" t="s">
+        <v>399</v>
+      </c>
+      <c r="G110" t="s">
+        <v>569</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G17"/>
+  <autoFilter ref="A1:G110"/>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1"/>
     <hyperlink ref="D2" r:id="rId2"/>
@@ -1125,6 +4677,192 @@
     <hyperlink ref="D16" r:id="rId30"/>
     <hyperlink ref="C17" r:id="rId31"/>
     <hyperlink ref="D17" r:id="rId32"/>
+    <hyperlink ref="C18" r:id="rId33"/>
+    <hyperlink ref="D18" r:id="rId34"/>
+    <hyperlink ref="C19" r:id="rId35"/>
+    <hyperlink ref="D19" r:id="rId36"/>
+    <hyperlink ref="C20" r:id="rId37"/>
+    <hyperlink ref="D20" r:id="rId38"/>
+    <hyperlink ref="C21" r:id="rId39"/>
+    <hyperlink ref="D21" r:id="rId40"/>
+    <hyperlink ref="C22" r:id="rId41"/>
+    <hyperlink ref="D22" r:id="rId42"/>
+    <hyperlink ref="C23" r:id="rId43"/>
+    <hyperlink ref="D23" r:id="rId44"/>
+    <hyperlink ref="C24" r:id="rId45"/>
+    <hyperlink ref="D24" r:id="rId46"/>
+    <hyperlink ref="C25" r:id="rId47"/>
+    <hyperlink ref="D25" r:id="rId48"/>
+    <hyperlink ref="C26" r:id="rId49"/>
+    <hyperlink ref="D26" r:id="rId50"/>
+    <hyperlink ref="C27" r:id="rId51"/>
+    <hyperlink ref="D27" r:id="rId52"/>
+    <hyperlink ref="C28" r:id="rId53"/>
+    <hyperlink ref="D28" r:id="rId54"/>
+    <hyperlink ref="C29" r:id="rId55"/>
+    <hyperlink ref="D29" r:id="rId56"/>
+    <hyperlink ref="C30" r:id="rId57"/>
+    <hyperlink ref="D30" r:id="rId58"/>
+    <hyperlink ref="C31" r:id="rId59"/>
+    <hyperlink ref="D31" r:id="rId60"/>
+    <hyperlink ref="C32" r:id="rId61"/>
+    <hyperlink ref="D32" r:id="rId62"/>
+    <hyperlink ref="C33" r:id="rId63"/>
+    <hyperlink ref="D33" r:id="rId64"/>
+    <hyperlink ref="C34" r:id="rId65"/>
+    <hyperlink ref="D34" r:id="rId66"/>
+    <hyperlink ref="C35" r:id="rId67"/>
+    <hyperlink ref="D35" r:id="rId68"/>
+    <hyperlink ref="C36" r:id="rId69"/>
+    <hyperlink ref="D36" r:id="rId70"/>
+    <hyperlink ref="C37" r:id="rId71"/>
+    <hyperlink ref="D37" r:id="rId72"/>
+    <hyperlink ref="C38" r:id="rId73"/>
+    <hyperlink ref="D38" r:id="rId74"/>
+    <hyperlink ref="C39" r:id="rId75"/>
+    <hyperlink ref="D39" r:id="rId76"/>
+    <hyperlink ref="C40" r:id="rId77"/>
+    <hyperlink ref="D40" r:id="rId78"/>
+    <hyperlink ref="C41" r:id="rId79"/>
+    <hyperlink ref="D41" r:id="rId80"/>
+    <hyperlink ref="C42" r:id="rId81"/>
+    <hyperlink ref="D42" r:id="rId82"/>
+    <hyperlink ref="C43" r:id="rId83"/>
+    <hyperlink ref="D43" r:id="rId84"/>
+    <hyperlink ref="C44" r:id="rId85"/>
+    <hyperlink ref="D44" r:id="rId86"/>
+    <hyperlink ref="C45" r:id="rId87"/>
+    <hyperlink ref="D45" r:id="rId88"/>
+    <hyperlink ref="C46" r:id="rId89"/>
+    <hyperlink ref="D46" r:id="rId90"/>
+    <hyperlink ref="C47" r:id="rId91"/>
+    <hyperlink ref="D47" r:id="rId92"/>
+    <hyperlink ref="C48" r:id="rId93"/>
+    <hyperlink ref="D48" r:id="rId94"/>
+    <hyperlink ref="C49" r:id="rId95"/>
+    <hyperlink ref="D49" r:id="rId96"/>
+    <hyperlink ref="C50" r:id="rId97"/>
+    <hyperlink ref="D50" r:id="rId98"/>
+    <hyperlink ref="C51" r:id="rId99"/>
+    <hyperlink ref="D51" r:id="rId100"/>
+    <hyperlink ref="C52" r:id="rId101"/>
+    <hyperlink ref="D52" r:id="rId102"/>
+    <hyperlink ref="C53" r:id="rId103"/>
+    <hyperlink ref="D53" r:id="rId104"/>
+    <hyperlink ref="C54" r:id="rId105"/>
+    <hyperlink ref="D54" r:id="rId106"/>
+    <hyperlink ref="C55" r:id="rId107"/>
+    <hyperlink ref="D55" r:id="rId108"/>
+    <hyperlink ref="C56" r:id="rId109"/>
+    <hyperlink ref="D56" r:id="rId110"/>
+    <hyperlink ref="C57" r:id="rId111"/>
+    <hyperlink ref="D57" r:id="rId112"/>
+    <hyperlink ref="C58" r:id="rId113"/>
+    <hyperlink ref="D58" r:id="rId114"/>
+    <hyperlink ref="C59" r:id="rId115"/>
+    <hyperlink ref="D59" r:id="rId116"/>
+    <hyperlink ref="C60" r:id="rId117"/>
+    <hyperlink ref="D60" r:id="rId118"/>
+    <hyperlink ref="C61" r:id="rId119"/>
+    <hyperlink ref="D61" r:id="rId120"/>
+    <hyperlink ref="C62" r:id="rId121"/>
+    <hyperlink ref="D62" r:id="rId122"/>
+    <hyperlink ref="C63" r:id="rId123"/>
+    <hyperlink ref="D63" r:id="rId124"/>
+    <hyperlink ref="C64" r:id="rId125"/>
+    <hyperlink ref="D64" r:id="rId126"/>
+    <hyperlink ref="C65" r:id="rId127"/>
+    <hyperlink ref="D65" r:id="rId128"/>
+    <hyperlink ref="C66" r:id="rId129"/>
+    <hyperlink ref="D66" r:id="rId130"/>
+    <hyperlink ref="C67" r:id="rId131"/>
+    <hyperlink ref="D67" r:id="rId132"/>
+    <hyperlink ref="C68" r:id="rId133"/>
+    <hyperlink ref="D68" r:id="rId134"/>
+    <hyperlink ref="C69" r:id="rId135"/>
+    <hyperlink ref="D69" r:id="rId136"/>
+    <hyperlink ref="C70" r:id="rId137"/>
+    <hyperlink ref="D70" r:id="rId138"/>
+    <hyperlink ref="C71" r:id="rId139"/>
+    <hyperlink ref="D71" r:id="rId140"/>
+    <hyperlink ref="C72" r:id="rId141"/>
+    <hyperlink ref="D72" r:id="rId142"/>
+    <hyperlink ref="C73" r:id="rId143"/>
+    <hyperlink ref="D73" r:id="rId144"/>
+    <hyperlink ref="C74" r:id="rId145"/>
+    <hyperlink ref="D74" r:id="rId146"/>
+    <hyperlink ref="C75" r:id="rId147"/>
+    <hyperlink ref="D75" r:id="rId148"/>
+    <hyperlink ref="C76" r:id="rId149"/>
+    <hyperlink ref="D76" r:id="rId150"/>
+    <hyperlink ref="C77" r:id="rId151"/>
+    <hyperlink ref="D77" r:id="rId152"/>
+    <hyperlink ref="C78" r:id="rId153"/>
+    <hyperlink ref="D78" r:id="rId154"/>
+    <hyperlink ref="C79" r:id="rId155"/>
+    <hyperlink ref="D79" r:id="rId156"/>
+    <hyperlink ref="C80" r:id="rId157"/>
+    <hyperlink ref="D80" r:id="rId158"/>
+    <hyperlink ref="C81" r:id="rId159"/>
+    <hyperlink ref="D81" r:id="rId160"/>
+    <hyperlink ref="C82" r:id="rId161"/>
+    <hyperlink ref="D82" r:id="rId162"/>
+    <hyperlink ref="C83" r:id="rId163"/>
+    <hyperlink ref="D83" r:id="rId164"/>
+    <hyperlink ref="C84" r:id="rId165"/>
+    <hyperlink ref="D84" r:id="rId166"/>
+    <hyperlink ref="C85" r:id="rId167"/>
+    <hyperlink ref="D85" r:id="rId168"/>
+    <hyperlink ref="C86" r:id="rId169"/>
+    <hyperlink ref="D86" r:id="rId170"/>
+    <hyperlink ref="C87" r:id="rId171"/>
+    <hyperlink ref="D87" r:id="rId172"/>
+    <hyperlink ref="C88" r:id="rId173"/>
+    <hyperlink ref="D88" r:id="rId174"/>
+    <hyperlink ref="C89" r:id="rId175"/>
+    <hyperlink ref="D89" r:id="rId176"/>
+    <hyperlink ref="C90" r:id="rId177"/>
+    <hyperlink ref="D90" r:id="rId178"/>
+    <hyperlink ref="C91" r:id="rId179"/>
+    <hyperlink ref="D91" r:id="rId180"/>
+    <hyperlink ref="C92" r:id="rId181"/>
+    <hyperlink ref="D92" r:id="rId182"/>
+    <hyperlink ref="C93" r:id="rId183"/>
+    <hyperlink ref="D93" r:id="rId184"/>
+    <hyperlink ref="C94" r:id="rId185"/>
+    <hyperlink ref="D94" r:id="rId186"/>
+    <hyperlink ref="C95" r:id="rId187"/>
+    <hyperlink ref="D95" r:id="rId188"/>
+    <hyperlink ref="C96" r:id="rId189"/>
+    <hyperlink ref="D96" r:id="rId190"/>
+    <hyperlink ref="C97" r:id="rId191"/>
+    <hyperlink ref="D97" r:id="rId192"/>
+    <hyperlink ref="C98" r:id="rId193"/>
+    <hyperlink ref="D98" r:id="rId194"/>
+    <hyperlink ref="C99" r:id="rId195"/>
+    <hyperlink ref="D99" r:id="rId196"/>
+    <hyperlink ref="C100" r:id="rId197"/>
+    <hyperlink ref="D100" r:id="rId198"/>
+    <hyperlink ref="C101" r:id="rId199"/>
+    <hyperlink ref="D101" r:id="rId200"/>
+    <hyperlink ref="C102" r:id="rId201"/>
+    <hyperlink ref="D102" r:id="rId202"/>
+    <hyperlink ref="C103" r:id="rId203"/>
+    <hyperlink ref="D103" r:id="rId204"/>
+    <hyperlink ref="C104" r:id="rId205"/>
+    <hyperlink ref="D104" r:id="rId206"/>
+    <hyperlink ref="C105" r:id="rId207"/>
+    <hyperlink ref="D105" r:id="rId208"/>
+    <hyperlink ref="C106" r:id="rId209"/>
+    <hyperlink ref="D106" r:id="rId210"/>
+    <hyperlink ref="C107" r:id="rId211"/>
+    <hyperlink ref="D107" r:id="rId212"/>
+    <hyperlink ref="C108" r:id="rId213"/>
+    <hyperlink ref="D108" r:id="rId214"/>
+    <hyperlink ref="C109" r:id="rId215"/>
+    <hyperlink ref="D109" r:id="rId216"/>
+    <hyperlink ref="C110" r:id="rId217"/>
+    <hyperlink ref="D110" r:id="rId218"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
